--- a/data-vh/Май_2026_ВХ.xlsx
+++ b/data-vh/Май_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$35</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,2420 +562,2569 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="22.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000062</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>06.05.2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001791 от 06.05.2026 14:48:21</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>ТЗ ООО (6320041310)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Переходник МФГ30-М 001.51.00.001  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Невыполнение технических требований КД</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Отсутствует притупление острых кромок радиусом 0,5 мм. (МФГ30-М 001.51.00.001 п.3)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены поставщиком.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="10.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция основная Э 662.00.15.000, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="9" t="n">
         <v>1.36</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="10.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция балки Э 662.00.00.001, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="9" t="n">
         <v>4.48</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="10.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Шайба Э 662.00.00.002, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="11" t="n">
         <v>0.116</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="10.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Пластина Э 662.00.00.003, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="10.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция деформационная №2, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="9" t="n">
         <v>1.76</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="22.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Основание ФО-У-80 (Э 662.00.06.000), Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="9" t="n">
         <v>4.26</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="10.95" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция деформационная №8, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="9" t="n">
         <v>2.24</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" ht="10.95" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Плита начальная Э 662.00.12.001, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="9" t="n">
         <v>0.34</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" ht="22.95" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>В00-0000064</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000198 от 13.05.2026 13:53:20</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х445х545) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="9" t="n">
         <v>108.34</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>500±20 факт. 40,30 – 40,90;    500±20 факт. 38,60 – 39,70;    5±0,2 факт. 4,2-5,0.    Заусенцы.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>Доработано подрядчиком</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" ht="22.95" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>В00-0000064</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000198 от 13.05.2026 13:53:20</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х454х470) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>55±0,4 факт. 63;    500±20 факт. 400;    5±0,2 факт. 4,2-5,0.    Заусенцы.    Несоответствующее формообразование левой торцевой поверхности, вид В.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>Доработано подрядчиком</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" ht="22.95" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>В00-0000064</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000198 от 13.05.2026 13:53:20</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х454х470) зеркальная (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>5±0,2 факт. 4,2-5,0.    Заусенцы.</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>Доработано подрядчиком</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" ht="22.95" customHeight="1">
+      <c r="A14" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>В00-0000065</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>14.05.2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001899 от 14.05.2026 10:55:15</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Строд Сервис (Самара) (ЭДО Такском ЗП 06.02.25)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>_уу_(ПРАВАЯ) Пленка для демпферного устройства ФО-2 фон+Сегмент 1(1шт)+Сегмент 1(2шт) (белая, черная</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>1.2.1.5 Световозвращающие пленки</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>Поставщик произвел замену пленки.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" ht="34.95" customHeight="1">
+      <c r="A15" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>В00-0000067</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>14.05.2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001898 от 14.05.2026 10:51:53</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>ОБЕСПЕЧЕНИЕ фирма ООО</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>_уу_Отвод 90-1-114,3х6,3 ГОСТ 17375-2001/Ст10</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>Детали трубопроводов 3D ГОСТ 17375-2001</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 17380 табл. 3 Размер 6,3-0,8 мм, фактически 5,0-5,6 мм.</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>Конструктором оформлено Разрешение на отступление от чертежа 01/КП 1760, КП 2274. Взять в работу в штатном режиме.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" ht="70.95" customHeight="1">
+      <c r="A16" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>В00-0000068</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>14.05.2026</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000201 от 14.05.2026 12:38:43</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Корпус №07</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="9" t="n">
         <v>16.24</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>Шаг несущей полосы 34 ± 1,5 мм, фактически 29 – 41 мм.    Р-р 746-2 фактически 742 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла).    Сварка связующих элементов с крайними несущими полосами выполнена на прихватках.     Максимальное выступание связующих элементов над несущими полосами не более 1,5 мм, фактически 3 мм.    Дефекты сварных швов:    Несплавления связующих полос с несущими.    Брызги металла, наплывы.</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников УПН</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" ht="82.05" customHeight="1">
+      <c r="A17" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>В00-0000069</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>15.05.2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>М-СТАЛЬ ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>М-СТАЛЬ ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>(ПФ) Четверть вторая (четвертая) оболочки нижней секции (раскрой)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="9" t="n">
         <v>388.55</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>1.Геометрические размеры:    Размер 482±2 – факт. 478;    Размер 868±2 – факт. 864;    Паз 14+0,5х90+1 – факт 14,9х90;    Отверстие ф25+2 – факт. 24,5;    Пазы 5±1х5±1х5±1 – факт. 5х3х3.    2.Отклонения от плоскостности детали:    Условная вершина условного нижнего    основания трапеции – 9 мм;    Нижняя часть трапеции – 6 мм;    Центральная часть трапеции – 3 мм;    По условным граням (линии гиба) слева    направо – 7; 10; 7;5.    3.Дефекты термической резки:    Цепочки застывших капель, облой, шлак,    выхватывания.</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>Изготовление опытного образца</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" ht="82.05" customHeight="1">
+      <c r="A18" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>В00-0000070</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>19.05.2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000205 от 18.05.2026 15:11:01</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="8" t="n">
         <v>243.6</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>Р-р 746-2 фактически 743 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла). Выступание связующих элементов по СТО не более 1,5мм, фактически до 4мм. Занижение обрамляющего элемента по СТО не более 1мм, фактически до 4мм. Выступание обрамляющего элемента по СТО не более 1мм, фактически до 4мм. Выгнутость по СТО не более 3мм, фактически до 5мм. Механические повреждения. Дефекты сварных швов: брызги металла, кратеры, поры, натёки, прожоги, несплавления.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="Q18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="34.95" customHeight="1">
+      <c r="A19" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>В00-0000071</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>20.05.2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002037 от 19.05.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>МЕТИЗКОМПЛЕКТ ПК ООО(ЭДО Такском ЗП согл. от 01.04.2026)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>БЕЗ МАРКИРОВКИ_ГПЦ(закупка) Болт М16-6azx60.58.0940 ГОСТ 7802-81 Оцинкованное</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>Метизы</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="12" t="n">
         <v>1900</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="8" t="n">
         <v>229.9</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Отсутствует маркировка класса прочности. Диаметр головки по ГОСТ7802  35+-0.8мм, фактически 37,28-37,96мм. Высота головки по ГОСТ 7802 8+-0,45мм, фактически 10мм. Неполный профиль резьбы.</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>Письмо Снегирев</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" ht="22.95" customHeight="1">
+      <c r="A20" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>В00-0000071</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>20.05.2026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002037 от 19.05.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>МЕТИЗКОМПЛЕКТ ПК ООО(ЭДО Такском ЗП согл. от 01.04.2026)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>ГПЦ(закупка) (в ШТ) Гайка М16-6H.6.0930 ГОСТ 5915-70 Оцинкованное</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>Метизы</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Высота гайки по ГОСТ 5915 14,8-1,1мм, фактически 12,84-12,99мм.</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>Письмо Снегирев</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" ht="34.95" customHeight="1">
+      <c r="A21" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>В00-0000072</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>22.05.2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000221 от 21.05.2026 16:47:49</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="14" t="n">
         <v>6990.4</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ:    Не выполнено требование "Заварить"         Дефекты сварных швов:    брызги металла, подрезы, шлак, несплавление.        Дефекты лазерной резки: незавершенный рез, налипший шлак.</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" ht="22.95" customHeight="1">
+      <c r="A22" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>В00-0000073</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>22.05.2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000223 от 22.05.2026 13:04:19</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="14" t="n">
         <v>3495.2</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ:Не выполнено требование "Заварить". Дефекты сварных швов: брызги металла, подрезы, шлак, несплавление, остатки сварочной проволоки.</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" ht="22.95" customHeight="1">
+      <c r="A23" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>В00-0000074</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>23.05.2026</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000225 от 23.05.2026 8:39:12</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Опора МСО-ФГ-7-9-01 СТО 07525912-300-2021 (ФГС-700-9,0-01) (ОО 345.00.00.000 СБ)  (от п</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="10" t="n">
         <v>3890.25</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>Брызги металла. Несплавления. Остатки сварочной проволоки.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="Q23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="58.95" customHeight="1">
+      <c r="A24" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>В00-0000075</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>23.05.2026</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000226 от 23.05.2026 12:44:03</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="10" t="n">
         <v>1546.95</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Малозначительное Неустранимое</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>Размер 2380+-2мм, фактически 2384мм (1шт). Размер кромки 100+1мм, фактически 199мм. Размер до тех. отверстия 35+-1мм, фактически 30мм (2шт). Размер между тех. отверстиями 770+-1мм, фактически 770мм, 685мм, 871мм (2шт). Размер кромки 15+-1мм, фактически 13-15мм Отсутствует кромка 20+-0,3*3+-1.Размер 55+-0,4мм, фактически 53,69-56,81мм. Заусенцы. Остатки силиконового герметика..</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников ОЭУ</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" ht="46.95" customHeight="1">
+      <c r="A25" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>В00-0000076</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>25.05.2026</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000232 от 25.05.2026 8:18:56</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Опора МСО-ФГ-7-9-01 СТО 07525912-300-2021 (ФГС-700-9,0-01) (ОО 345.00.00.000 СБ)  (от п</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="12" t="n">
         <v>1482</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: остатки сварочной проволоки, брызги металла, несплавления, кратеры, поры, неравномерная ширина шва, плохое повторное возбуждение дуги. Не выполнено требование "Заварить". Дефекты лазерной резки: налипший шлак, незавершённый рез .</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="Q25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="34.95" customHeight="1">
+      <c r="A26" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>В00-0000077</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002106 от 25.05.2026 13:23:44</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>ТД ЭЛЕКТРОТЕХМОНТАЖ АО (ЭТМ)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>_уу_Шкаф распределительный ЩВ1+ЩВ2 по М 038.00.00.000 ЭЗ</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД.</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>Карточка разрешения № 46 от 28.05.2026. Прошу допустить в дальнейшее производство работ без доработок по карточке разрешения.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" ht="22.95" customHeight="1">
+      <c r="A27" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>В00-0000078</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000247 от 26.05.2026 16:46:13</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="14" t="n">
         <v>10485.6</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>Не выполнено требование "Заварить". По КД сварной шов №2 между деталью 2 (ребро) и деталью 3 (фланец) катет 8, фактически 6 (1шт). Брызги металла (1 шт).</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" ht="58.95" customHeight="1">
+      <c r="A28" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>В00-0000079</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000246 от 26.05.2026 14:39:35</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="9" t="n">
         <v>928.17</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>1.Размер 40±0,3 мм, фактически 38-40 мм.    2.Размер 100+1 мм, фактически 119-120 мм.    2. Размер 5±0,2 мм фактически 4,1-4,3 мм (на одной пластине).    3.Отсутствует кромка 20±0,3*3±1 мм.     4.Профиль фаски 15х25˚ не соответствует заданному на Ц 184.04.00.001 выносной элемент Б. Подрезание (местное углубление на обработанной поверхности) до 1 мм на длине 100 мм - 2380 мм.    5.Заусенцы.</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>КР №50 от 02.06.2026, Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" ht="58.95" customHeight="1">
+      <c r="A29" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>В00-0000079</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000246 от 26.05.2026 14:39:35</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2385) зеркальная (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="9" t="n">
         <v>310.04</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>1.Размер 40±0,3 мм, фактически 38-40 мм.    2.Размер 100+1 мм, фактически 119-120 мм.    3.Отсутствует кромка 20±0,3*3±1 мм.     4.Профиль фаски 15х250 не соответствует заданному на Ц 184.04.00.001 выносной элемент Б. Подрезание (местное углубление на обработанной поверхности) до 1 мм на длине 100 мм - 2385 мм.    5.Заусенцы.</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>КР №50 от 02.06.2026, Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" ht="70.95" customHeight="1">
+      <c r="A30" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>В00-0000079</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000246 от 26.05.2026 14:39:35</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2385) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="9" t="n">
         <v>310.04</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>Фактически пластина 32х570х2380 мм.    1.Размер 40±0,3 мм, фактически 38-40 мм.    2.Размер 100+1 мм, фактически 119-120 мм.    3.Отсутствует кромка 20±0,3*3±1 мм.     4.Профиль фаски 15х250 не соответствует заданному на Ц 184.05.00.001-01 выносной элемент Б. Подрезание (местное углубление на обработанной поверхности) до 1 мм на длине 100 мм - 2380 мм.    5.Заусенцы.    6.Дефект плазменной резки – незавершенный рез.</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>КР №50 от 02.06.2026, Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" ht="22.95" customHeight="1">
+      <c r="A31" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>В00-0000080</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>_Склад корпус №8</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="14" t="n">
         <v>6990.4</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ: Не выполнено требование "Заварить".</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" ht="22.95" customHeight="1">
+      <c r="A32" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>В00-0000081</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000243 от 26.05.2026 10:31:31</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР8 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="10" t="n">
         <v>4054.25</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="Q32" s="7" t="n"/>
+    </row>
+    <row r="33" ht="22.95" customHeight="1">
+      <c r="A33" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>В00-0000081</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000243 от 26.05.2026 10:31:31</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР19 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="10" t="n">
         <v>1024.26</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="Q33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="70.95" customHeight="1">
+      <c r="A34" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>В00-0000082</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>28.05.2026</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000256 от 27.05.2026 18:42:52</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="10" t="n">
         <v>2338.56</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>По СТО выступание связующих элементов над несущими полосами не более 1,5мм, фактически до 3,4мм. По СТО занижение обрамляющего элемента относительно несущей полосы не более 1мм, фактически до 5мм. Р-р 746-2 фактически 742 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла). Механические повреждения. Дефекты сварки: несплавления, натёки, поры, прожог (1шт), остатки сварочной проволоки (1шт).</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>КР 51 от 02.06.2026, несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" ht="22.95" customHeight="1">
+      <c r="A35" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>В00-0000083</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>30.05.2026</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000260 от 28.05.2026 14:43:31</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="8" t="n">
         <v>873.8</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>1. Подрезы. 2. Брызги металла. 3. Незавареный кратер. 4. Не выполнено требование "Заварить".</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q35">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="35">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>